--- a/artfynd/A 60-2022 artfynd.xlsx
+++ b/artfynd/A 60-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 60-2022 artfynd.xlsx
+++ b/artfynd/A 60-2022 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>2206381</v>
       </c>
       <c r="B2" t="n">
-        <v>104489</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107609</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>690712.1134613418</v>
+        <v>690712</v>
       </c>
       <c r="R2" t="n">
-        <v>6611889.639335149</v>
+        <v>6611890</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -748,19 +743,9 @@
           <t>2007-05-20</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2007-05-31</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -795,16 +780,11 @@
         <v>3924730</v>
       </c>
       <c r="B3" t="n">
-        <v>99397</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>102241</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -832,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>690712.1134613418</v>
+        <v>690712</v>
       </c>
       <c r="R3" t="n">
-        <v>6611889.639335149</v>
+        <v>6611890</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -865,19 +845,9 @@
           <t>2007-05-20</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2007-05-31</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
